--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R5" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B6" t="n">
-        <v>97320</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R6" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>97321</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R5" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>97321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R6" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350417</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350419</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127350413</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127350405</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127350415</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127350418</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350417</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350419</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127350413</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R5" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R6" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1163,7 +1163,7 @@
         <v>127350405</v>
       </c>
       <c r="B7" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127350415</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127350418</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R5" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R6" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350417</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350419</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127350413</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127350405</v>
       </c>
       <c r="B7" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127350415</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127350418</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127350417</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127350419</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127350413</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>127350405</v>
       </c>
       <c r="B7" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>127350415</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>127350418</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>97345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R5" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B6" t="n">
-        <v>97345</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R6" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>127350406</v>
       </c>
       <c r="B5" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350406</v>
+        <v>127350420</v>
       </c>
       <c r="B5" t="n">
-        <v>97346</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863823</v>
+        <v>863845</v>
       </c>
       <c r="R5" t="n">
-        <v>7421616</v>
+        <v>7421663</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350420</v>
+        <v>127350406</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863845</v>
+        <v>863823</v>
       </c>
       <c r="R6" t="n">
-        <v>7421663</v>
+        <v>7421616</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127350417</v>
+        <v>127350413</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>863773</v>
+        <v>863858</v>
       </c>
       <c r="R2" t="n">
-        <v>7421711</v>
+        <v>7421580</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127350419</v>
+        <v>127350415</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>863884</v>
+        <v>863836</v>
       </c>
       <c r="R3" t="n">
-        <v>7421687</v>
+        <v>7421609</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127350413</v>
+        <v>127350417</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>863858</v>
+        <v>863773</v>
       </c>
       <c r="R4" t="n">
-        <v>7421580</v>
+        <v>7421711</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127350420</v>
+        <v>127350418</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>863845</v>
+        <v>863878</v>
       </c>
       <c r="R5" t="n">
-        <v>7421663</v>
+        <v>7421748</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127350406</v>
+        <v>127350419</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>863823</v>
+        <v>863884</v>
       </c>
       <c r="R6" t="n">
-        <v>7421616</v>
+        <v>7421687</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127350405</v>
+        <v>127350420</v>
       </c>
       <c r="B7" t="n">
-        <v>57669</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>863886</v>
+        <v>863845</v>
       </c>
       <c r="R7" t="n">
-        <v>7421700</v>
+        <v>7421663</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1231,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-09</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127350415</v>
+        <v>127350405</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>863836</v>
+        <v>863886</v>
       </c>
       <c r="R8" t="n">
-        <v>7421609</v>
+        <v>7421700</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1333,6 +1328,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-09</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127350418</v>
+        <v>127350406</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>863878</v>
+        <v>863823</v>
       </c>
       <c r="R9" t="n">
-        <v>7421748</v>
+        <v>7421616</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>

--- a/artfynd/A 47126-2023 artfynd.xlsx
+++ b/artfynd/A 47126-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350413</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350415</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350417</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350418</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350419</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350420</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,8 +1493,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350406</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>